--- a/Team-Data/2014-15/12-18-2014-15.xlsx
+++ b/Team-Data/2014-15/12-18-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,22 +806,22 @@
         <v>6</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
         <v>7</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
@@ -769,31 +836,31 @@
         <v>8</v>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -927,7 +994,7 @@
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
         <v>21</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
@@ -975,7 +1042,7 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
         <v>19</v>
@@ -1121,13 +1188,13 @@
         <v>22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM4" t="n">
         <v>19</v>
@@ -1148,10 +1215,10 @@
         <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
         <v>19</v>
@@ -1172,10 +1239,10 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>26</v>
@@ -1303,7 +1370,7 @@
         <v>20</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
@@ -1315,7 +1382,7 @@
         <v>26</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>25</v>
@@ -1333,7 +1400,7 @@
         <v>17</v>
       </c>
       <c r="AT5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU5" t="n">
         <v>21</v>
@@ -1345,7 +1412,7 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY5" t="n">
         <v>9</v>
@@ -1360,7 +1427,7 @@
         <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
         <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.64</v>
+        <v>0.625</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J6" t="n">
-        <v>81.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.455</v>
       </c>
       <c r="L6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M6" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.363</v>
+        <v>0.356</v>
       </c>
       <c r="O6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P6" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q6" t="n">
         <v>0.764</v>
@@ -1434,10 +1501,10 @@
         <v>10.9</v>
       </c>
       <c r="S6" t="n">
-        <v>33.8</v>
+        <v>34.4</v>
       </c>
       <c r="T6" t="n">
-        <v>44.8</v>
+        <v>45.3</v>
       </c>
       <c r="U6" t="n">
         <v>22.3</v>
@@ -1446,58 +1513,58 @@
         <v>15</v>
       </c>
       <c r="W6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
         <v>4.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
         <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM6" t="n">
         <v>18</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>3</v>
@@ -1512,10 +1579,10 @@
         <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>11</v>
@@ -1524,13 +1591,13 @@
         <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ6" t="n">
         <v>8</v>
@@ -1542,7 +1609,7 @@
         <v>14</v>
       </c>
       <c r="BC6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>3</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1667,7 +1734,7 @@
         <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK7" t="n">
         <v>10</v>
@@ -1676,16 +1743,16 @@
         <v>11</v>
       </c>
       <c r="AM7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
@@ -1697,7 +1764,7 @@
         <v>22</v>
       </c>
       <c r="AT7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU7" t="n">
         <v>10</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -1753,64 +1820,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
         <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.731</v>
+        <v>0.704</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="J8" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.48</v>
+        <v>0.481</v>
       </c>
       <c r="L8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
         <v>17.9</v>
       </c>
       <c r="P8" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R8" t="n">
         <v>11.3</v>
       </c>
       <c r="S8" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W8" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X8" t="n">
         <v>5.3</v>
@@ -1822,28 +1889,28 @@
         <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>110.5</v>
+        <v>110.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1861,25 +1928,25 @@
         <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
         <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
         <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1891,16 +1958,16 @@
         <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ8" t="n">
         <v>10</v>
       </c>
       <c r="BA8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -2013,13 +2080,13 @@
         <v>-2</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
         <v>20</v>
@@ -2037,7 +2104,7 @@
         <v>25</v>
       </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
         <v>6</v>
@@ -2046,13 +2113,13 @@
         <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP9" t="n">
         <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -2213,19 +2280,19 @@
         <v>27</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM10" t="n">
         <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2240,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -2299,64 +2366,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>40.6</v>
+        <v>40.3</v>
       </c>
       <c r="J11" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.48</v>
+        <v>0.478</v>
       </c>
       <c r="L11" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O11" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.781</v>
+        <v>0.784</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>35.5</v>
+        <v>35.8</v>
       </c>
       <c r="T11" t="n">
-        <v>45.6</v>
+        <v>45.8</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="W11" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X11" t="n">
         <v>6.7</v>
@@ -2365,19 +2432,19 @@
         <v>3.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>107.5</v>
+        <v>107.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,13 +2456,13 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
         <v>3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
         <v>3</v>
@@ -2410,13 +2477,13 @@
         <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
         <v>25</v>
@@ -2443,13 +2510,13 @@
         <v>4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -2484,13 +2551,13 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.75</v>
+        <v>0.792</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
@@ -2499,76 +2566,76 @@
         <v>34.8</v>
       </c>
       <c r="J12" t="n">
-        <v>82.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.424</v>
+        <v>0.426</v>
       </c>
       <c r="L12" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>25.7</v>
+        <v>26.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.714</v>
+        <v>0.709</v>
       </c>
       <c r="R12" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S12" t="n">
         <v>32.3</v>
       </c>
       <c r="T12" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U12" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="W12" t="n">
         <v>9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>3</v>
       </c>
       <c r="AG12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
@@ -2577,10 +2644,10 @@
         <v>28</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
@@ -2592,10 +2659,10 @@
         <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2607,7 +2674,7 @@
         <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
         <v>29</v>
@@ -2622,19 +2689,19 @@
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
         <v>18</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2814,7 @@
         <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
         <v>24</v>
@@ -2756,16 +2823,16 @@
         <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>17</v>
@@ -2783,10 +2850,10 @@
         <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>2</v>
@@ -2795,7 +2862,7 @@
         <v>24</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
@@ -2804,7 +2871,7 @@
         <v>18</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>17</v>
@@ -2813,7 +2880,7 @@
         <v>19</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -2923,19 +2990,19 @@
         <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>8</v>
@@ -2956,13 +3023,13 @@
         <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
         <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>29</v>
@@ -2986,7 +3053,7 @@
         <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ14" t="n">
         <v>18</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -3027,85 +3094,85 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="J15" t="n">
-        <v>87.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.439</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="O15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>26.1</v>
+        <v>26.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R15" t="n">
         <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T15" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U15" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V15" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.7</v>
+        <v>102.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.9</v>
+        <v>-7.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -3117,10 +3184,10 @@
         <v>23</v>
       </c>
       <c r="AH15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>3</v>
@@ -3129,7 +3196,7 @@
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM15" t="n">
         <v>23</v>
@@ -3138,19 +3205,19 @@
         <v>19</v>
       </c>
       <c r="AO15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP15" t="n">
         <v>5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT15" t="n">
         <v>16</v>
@@ -3159,13 +3226,13 @@
         <v>22</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY15" t="n">
         <v>6</v>
@@ -3174,13 +3241,13 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>6.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>2</v>
@@ -3317,7 +3384,7 @@
         <v>28</v>
       </c>
       <c r="AN16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -3475,10 +3542,10 @@
         <v>15</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
         <v>28</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
         <v>12</v>
@@ -3499,7 +3566,7 @@
         <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>11</v>
@@ -3535,13 +3602,13 @@
         <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>14</v>
       </c>
       <c r="BB17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC17" t="n">
         <v>22</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -3573,55 +3640,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
         <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.519</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I18" t="n">
         <v>37.6</v>
       </c>
       <c r="J18" t="n">
-        <v>81.2</v>
+        <v>81.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P18" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0.783</v>
       </c>
       <c r="R18" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="U18" t="n">
         <v>22.2</v>
@@ -3630,31 +3697,31 @@
         <v>16.8</v>
       </c>
       <c r="W18" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
@@ -3669,10 +3736,10 @@
         <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
         <v>14</v>
@@ -3690,16 +3757,16 @@
         <v>19</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU18" t="n">
         <v>12</v>
@@ -3714,13 +3781,13 @@
         <v>26</v>
       </c>
       <c r="AY18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>27</v>
@@ -3848,10 +3915,10 @@
         <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3875,13 +3942,13 @@
         <v>27</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>14</v>
@@ -3896,7 +3963,7 @@
         <v>25</v>
       </c>
       <c r="AY19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ19" t="n">
         <v>16</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -3952,70 +4019,70 @@
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="J20" t="n">
-        <v>84.7</v>
+        <v>85.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.467</v>
+        <v>0.464</v>
       </c>
       <c r="L20" t="n">
         <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O20" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.755</v>
+        <v>0.737</v>
       </c>
       <c r="R20" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T20" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="U20" t="n">
         <v>21.9</v>
       </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>20.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>103.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>15</v>
@@ -4024,7 +4091,7 @@
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
@@ -4033,7 +4100,7 @@
         <v>4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK20" t="n">
         <v>7</v>
@@ -4042,55 +4109,55 @@
         <v>21</v>
       </c>
       <c r="AM20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN20" t="n">
         <v>17</v>
       </c>
       <c r="AO20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>13</v>
       </c>
       <c r="AV20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX20" t="n">
         <v>3</v>
       </c>
-      <c r="AW20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>5</v>
-      </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>7</v>
       </c>
       <c r="BC20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.179</v>
+        <v>0.185</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J21" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L21" t="n">
         <v>7.2</v>
       </c>
       <c r="M21" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.368</v>
+        <v>0.363</v>
       </c>
       <c r="O21" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="P21" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="Q21" t="n">
         <v>0.788</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S21" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T21" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U21" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="n">
         <v>15.2</v>
@@ -4179,31 +4246,31 @@
         <v>7</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z21" t="n">
         <v>23.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC21" t="n">
         <v>-6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>27</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG21" t="n">
         <v>29</v>
@@ -4224,10 +4291,10 @@
         <v>17</v>
       </c>
       <c r="AM21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4239,7 +4306,7 @@
         <v>3</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4257,16 +4324,16 @@
         <v>20</v>
       </c>
       <c r="AX21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>27</v>
       </c>
-      <c r="AY21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>28</v>
-      </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -4301,136 +4368,136 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
         <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>0.462</v>
+        <v>0.48</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J22" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L22" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.318</v>
+        <v>0.313</v>
       </c>
       <c r="O22" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P22" t="n">
         <v>23.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="R22" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S22" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T22" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U22" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V22" t="n">
         <v>15.8</v>
       </c>
       <c r="W22" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>96.2</v>
+        <v>95.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
         <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
       </c>
       <c r="AL22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>18</v>
       </c>
-      <c r="AM22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>19</v>
-      </c>
       <c r="AR22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV22" t="n">
         <v>25</v>
@@ -4442,16 +4509,16 @@
         <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ22" t="n">
         <v>29</v>
       </c>
       <c r="BA22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC22" t="n">
         <v>13</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -4483,85 +4550,85 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>0.37</v>
+        <v>0.357</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.37</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="P23" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="R23" t="n">
+        <v>9</v>
+      </c>
+      <c r="S23" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="U23" t="n">
         <v>19.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="R23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S23" t="n">
-        <v>32</v>
-      </c>
-      <c r="T23" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>19.2</v>
-      </c>
       <c r="V23" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W23" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA23" t="n">
         <v>19</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>93.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>19</v>
@@ -4582,13 +4649,13 @@
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
@@ -4606,37 +4673,37 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AT23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AU23" t="n">
         <v>30</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4761,7 +4828,7 @@
         <v>30</v>
       </c>
       <c r="AJ24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK24" t="n">
         <v>30</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>9</v>
@@ -4785,10 +4852,10 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT24" t="n">
         <v>19</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
         <v>24</v>
@@ -4812,7 +4879,7 @@
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -4928,25 +4995,25 @@
         <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI25" t="n">
         <v>10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
@@ -4955,10 +5022,10 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -5113,10 +5180,10 @@
         <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH26" t="n">
         <v>28</v>
@@ -5128,7 +5195,7 @@
         <v>5</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5137,7 +5204,7 @@
         <v>7</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5149,7 +5216,7 @@
         <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS26" t="n">
         <v>2</v>
@@ -5179,7 +5246,7 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -5211,91 +5278,91 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>0.423</v>
+        <v>0.44</v>
       </c>
       <c r="H27" t="n">
         <v>48.8</v>
       </c>
       <c r="I27" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J27" t="n">
-        <v>78.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.456</v>
+        <v>0.452</v>
       </c>
       <c r="L27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M27" t="n">
         <v>14.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.332</v>
+        <v>0.329</v>
       </c>
       <c r="O27" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="P27" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R27" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="S27" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T27" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="V27" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="W27" t="n">
         <v>6</v>
       </c>
       <c r="X27" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z27" t="n">
         <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.8</v>
+        <v>100.6</v>
       </c>
       <c r="AC27" t="n">
         <v>-0.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>18</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AG27" t="n">
         <v>18</v>
@@ -5307,10 +5374,10 @@
         <v>26</v>
       </c>
       <c r="AJ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,25 +5398,25 @@
         <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.64</v>
+        <v>0.654</v>
       </c>
       <c r="H28" t="n">
         <v>49</v>
@@ -5411,67 +5478,67 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.374</v>
+        <v>0.38</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P28" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R28" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="T28" t="n">
-        <v>44.8</v>
+        <v>44.6</v>
       </c>
       <c r="U28" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X28" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y28" t="n">
         <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>10</v>
@@ -5483,34 +5550,34 @@
         <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>16</v>
       </c>
       <c r="AK28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM28" t="n">
         <v>13</v>
       </c>
-      <c r="AL28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>15</v>
-      </c>
       <c r="AN28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>24</v>
@@ -5519,16 +5586,16 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -5659,10 +5726,10 @@
         <v>3</v>
       </c>
       <c r="AF29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
         <v>13</v>
@@ -5683,13 +5750,13 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
         <v>2</v>
       </c>
       <c r="AP29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
@@ -5701,31 +5768,31 @@
         <v>23</v>
       </c>
       <c r="AT29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
         <v>18</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ29" t="n">
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC29" t="n">
         <v>2</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -5853,13 +5920,13 @@
         <v>23</v>
       </c>
       <c r="AJ30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM30" t="n">
         <v>20</v>
@@ -5874,16 +5941,16 @@
         <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>13</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>23</v>
@@ -5892,16 +5959,16 @@
         <v>19</v>
       </c>
       <c r="AW30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA30" t="n">
         <v>23</v>
@@ -5910,7 +5977,7 @@
         <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>4.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG31" t="n">
         <v>6</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>5</v>
       </c>
       <c r="AH31" t="n">
         <v>8</v>
@@ -6041,7 +6108,7 @@
         <v>4</v>
       </c>
       <c r="AL31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM31" t="n">
         <v>27</v>
@@ -6056,10 +6123,10 @@
         <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>9</v>
@@ -6077,7 +6144,7 @@
         <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-18-2014-15</t>
+          <t>2014-12-18</t>
         </is>
       </c>
     </row>
